--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -16,22 +16,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <x:si>
-    <x:t>Id</x:t>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>아이디</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap</x:t>
+    <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
@@ -40,10 +43,7 @@
     <x:t>Map_Basic_01</x:t>
   </x:si>
   <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵</x:t>
+    <x:t>Prefabs/Map/BasicMap</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -198,6 +198,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -280,6 +281,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -314,6 +316,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -358,6 +361,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -401,6 +405,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -485,26 +490,28 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -535,6 +542,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1249,13 +1257,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1265,13 +1273,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1282,13 +1290,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1298,13 +1306,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="27708" windowHeight="10944"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="27708" windowHeight="10968"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -14,36 +14,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
   <x:si>
     <x:t>프리팹 경로</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 맵</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
   </x:si>
   <x:si>
     <x:t>아이디</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1246,6 +1261,7 @@
   <x:dimension ref="A1:I9"/>
   <x:sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
+    <x:col min="1" max="1" width="26.109375" customWidth="1"/>
     <x:col min="2" max="2" width="16.33203125" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="20.77734375" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1257,13 +1273,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1273,13 +1289,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1290,13 +1306,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1306,13 +1322,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1320,18 +1336,30 @@
       <x:c r="G4" s="6"/>
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="3"/>
-      <x:c r="C5" s="2"/>
+      <x:c r="A5" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="3"/>
-      <x:c r="C6" s="2"/>
+      <x:c r="A6" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,51 +14,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>Map_Preset_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>Map_Preset_02</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/PresetMap2</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Prefabs/Map/BasicMap</x:t>
   </x:si>
   <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>Prefabs/ArrivePortal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -213,7 +222,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -296,7 +304,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -331,7 +338,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -376,7 +382,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -420,7 +425,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -505,28 +509,26 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -557,7 +559,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1273,13 +1274,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1289,13 +1290,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1306,13 +1307,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1322,13 +1323,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1337,13 +1338,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1352,18 +1353,29 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2"/>
+    </x:row>
+    <x:row r="7" spans="1:3" customHeight="1">
+      <x:c r="A7" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="9:9" customHeight="1">
       <x:c r="I9" s="4"/>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,60 +14,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도착지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Portal_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_02</x:t>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/ArrivePortal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/PresetMap1</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Map/PresetMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/ArrivePortal</x:t>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -222,6 +240,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -304,6 +323,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -338,6 +358,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -382,6 +403,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -425,6 +447,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -509,26 +532,28 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -559,6 +584,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1274,13 +1300,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1290,13 +1316,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1307,13 +1333,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1323,13 +1349,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1338,13 +1364,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1353,13 +1379,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -1368,16 +1394,36 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:3" customHeight="1">
+      <x:c r="A8" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>17</x:v>
+      <x:c r="B8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="9:9" customHeight="1">
+    <x:row r="9" spans="1:9" customHeight="1">
+      <x:c r="A9" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="I9" s="4"/>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -16,76 +16,76 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <x:si>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefabs/Map/BasicMap3</x:t>
   </x:si>
   <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>아이디</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>도착지</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
+    <x:t>맵 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>기본 맵 2</x:t>
   </x:si>
   <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Portal_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>기본 맵 1</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
     <x:t>프리셋 맵 1</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/ArrivePortal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap2</x:t>
+    <x:t>Prefabs/Map/ArrivePortal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -240,7 +240,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -323,7 +322,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -358,7 +356,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -403,7 +400,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -447,7 +443,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -532,28 +527,26 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -584,7 +577,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1300,13 +1292,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1316,13 +1308,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1333,13 +1325,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1352,10 +1344,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1364,13 +1356,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1382,10 +1374,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -1394,35 +1386,35 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,7 +14,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/ArrivePortal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
+  </x:si>
   <x:si>
     <x:t>Prefabs/Map/PresetMap2</x:t>
   </x:si>
@@ -22,70 +103,7 @@
     <x:t>Prefabs/Map/BasicMap2</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Portal_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도착지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/ArrivePortal</x:t>
+    <x:t>Prefabs/Map/BasicMap4</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -240,6 +258,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -322,6 +341,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -356,6 +376,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -400,6 +421,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -443,6 +465,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -527,26 +550,28 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -577,6 +602,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1277,7 +1303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I9"/>
+  <x:dimension ref="A1:I11"/>
   <x:sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -1292,13 +1318,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1308,13 +1334,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1325,13 +1351,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1341,13 +1367,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1356,13 +1382,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1371,13 +1397,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -1386,37 +1412,59 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I9" s="4"/>
+    </x:row>
+    <x:row r="10" spans="1:3" customHeight="1">
+      <x:c r="A10" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I9" s="4"/>
+      <x:c r="C10" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3" customHeight="1">
+      <x:c r="A11" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,90 +14,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
   <x:si>
     <x:t>Map_Preset_02</x:t>
   </x:si>
   <x:si>
+    <x:t>Map_Basic_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>Map_Basic_01</x:t>
   </x:si>
   <x:si>
     <x:t>Map_Basic_02</x:t>
   </x:si>
   <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>Map_Portal_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Map_Basic_04</x:t>
-  </x:si>
-  <x:si>
     <x:t>Map_Basic_05</x:t>
   </x:si>
   <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도착지</x:t>
-  </x:si>
-  <x:si>
     <x:t>Prefabs/Map/ArrivePortal</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/BasicMap5</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefabs/Map/BasicMap3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap2</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/BasicMap2</x:t>
@@ -258,7 +270,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -341,7 +352,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -376,7 +386,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -421,7 +430,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -465,7 +473,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -550,28 +557,26 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -602,7 +607,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1303,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I11"/>
+  <x:dimension ref="A1:I12"/>
   <x:sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -1318,13 +1322,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1334,13 +1338,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1351,13 +1355,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1367,13 +1371,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1382,13 +1386,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1397,13 +1401,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -1412,58 +1416,69 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:3" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3" customHeight="1">
+      <x:c r="A12" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
